--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N105_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N105_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.24817121649259</v>
+        <v>10.27782782268005</v>
       </c>
       <c r="D2" t="n">
-        <v>63.04097502257063</v>
+        <v>10.24415844116773</v>
       </c>
       <c r="E2" t="n">
-        <v>6.106543984687097</v>
+        <v>0.9923133975116532</v>
       </c>
       <c r="F2" t="n">
-        <v>5.932552153087183</v>
+        <v>0.9640397248766677</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.03508324711839</v>
+        <v>8.293201027656739</v>
       </c>
       <c r="D3" t="n">
-        <v>51.17587071639627</v>
+        <v>8.316078991414393</v>
       </c>
       <c r="E3" t="n">
-        <v>6.106543984687097</v>
+        <v>0.9923133975116532</v>
       </c>
       <c r="F3" t="n">
-        <v>5.932552153087183</v>
+        <v>0.9640397248766677</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
